--- a/client/public/products/pack1-pm-essentials/rfp-compliance-matrix.xlsx
+++ b/client/public/products/pack1-pm-essentials/rfp-compliance-matrix.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -103,8 +103,32 @@
       <color rgb="FF01696F"/>
       <sz val="13"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0001696F"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF0D1B2A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -129,8 +153,13 @@
         <bgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0D1B2A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -138,6 +167,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E7EB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -149,7 +192,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -256,6 +299,26 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -265,7 +328,7 @@
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -359,6 +422,17 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -421,6 +495,107 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Compliance Status</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Compliance Matrix'!$B$6:$B$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Compliance Matrix'!$C$6:$C$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="2340000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -620,9 +795,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="B2:K37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="18" min="1" max="1"/>
@@ -635,9 +810,9 @@
     <col width="35" customWidth="1" style="18" min="8" max="8"/>
     <col width="16" customWidth="1" style="18" min="9" max="9"/>
     <col width="14" customWidth="1" style="18" min="10" max="10"/>
+    <col width="16" customWidth="1" style="19" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="30" customHeight="1" s="19">
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -652,7 +827,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="21.75" customHeight="1" s="19">
       <c r="B5" s="22" t="inlineStr">
         <is>
@@ -670,6 +844,15 @@
         <f>COUNTIF(G14:G33,"Compliant")</f>
         <v/>
       </c>
+      <c r="E6" s="39" t="inlineStr">
+        <is>
+          <t>% Complete</t>
+        </is>
+      </c>
+      <c r="F6" s="40">
+        <f>C6/C10</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="19">
       <c r="B7" s="23" t="inlineStr">
@@ -715,911 +898,993 @@
         <v/>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13" ht="21.75" customHeight="1" s="19"/>
+    <row r="13" ht="21.75" customHeight="1" s="19">
+      <c r="K13" s="41" t="inlineStr">
+        <is>
+          <t>Status Flag</t>
+        </is>
+      </c>
+    </row>
     <row r="14" ht="30" customHeight="1" s="19">
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>L-001</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>L.5.1.1</t>
         </is>
       </c>
-      <c r="D14" s="29" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>Cover Letter — Signed by authorized corporate official; identify offeror, CAGE code, UEI, address, and POC</t>
         </is>
       </c>
-      <c r="E14" s="28" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t>I — Admin</t>
         </is>
       </c>
-      <c r="F14" s="28" t="inlineStr">
+      <c r="F14" s="36" t="inlineStr">
         <is>
           <t>Vol I, Section 1.0</t>
         </is>
       </c>
-      <c r="G14" s="28" t="inlineStr">
+      <c r="G14" s="36" t="inlineStr">
         <is>
           <t>Compliant</t>
         </is>
       </c>
-      <c r="H14" s="29" t="inlineStr">
+      <c r="H14" s="37" t="inlineStr">
         <is>
           <t>Cover letter template finalized</t>
         </is>
       </c>
-      <c r="I14" s="28" t="inlineStr">
+      <c r="I14" s="36" t="inlineStr">
         <is>
           <t>Contracts Mgr</t>
         </is>
       </c>
-      <c r="J14" s="30" t="n">
+      <c r="J14" s="38" t="n">
         <v>46132</v>
       </c>
+      <c r="K14" s="42">
+        <f>IF(G14="Compliant","",IF(AND(G14&lt;&gt;"N/A",TODAY()&gt;J14),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="19">
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>L-002</t>
         </is>
       </c>
-      <c r="C15" s="28" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>L.5.1.2</t>
         </is>
       </c>
-      <c r="D15" s="29" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>Executive Summary — 5-page maximum; summarize technical approach, relevant experience, and key personnel</t>
         </is>
       </c>
-      <c r="E15" s="28" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t>I — Admin</t>
         </is>
       </c>
-      <c r="F15" s="28" t="inlineStr">
+      <c r="F15" s="36" t="inlineStr">
         <is>
           <t>Vol I, Section 2.0</t>
         </is>
       </c>
-      <c r="G15" s="28" t="inlineStr">
+      <c r="G15" s="36" t="inlineStr">
         <is>
           <t>Compliant</t>
         </is>
       </c>
-      <c r="H15" s="29" t="inlineStr">
+      <c r="H15" s="37" t="inlineStr">
         <is>
           <t>Draft complete; final review pending</t>
         </is>
       </c>
-      <c r="I15" s="28" t="inlineStr">
+      <c r="I15" s="36" t="inlineStr">
         <is>
           <t>Capture Lead</t>
         </is>
       </c>
-      <c r="J15" s="30" t="n">
+      <c r="J15" s="38" t="n">
         <v>46130</v>
       </c>
+      <c r="K15" s="42">
+        <f>IF(G15="Compliant","",IF(AND(G15&lt;&gt;"N/A",TODAY()&gt;J15),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="19">
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>L-003</t>
         </is>
       </c>
-      <c r="C16" s="28" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>L.5.2.1</t>
         </is>
       </c>
-      <c r="D16" s="29" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>Technical Approach — Describe methodology to meet SOW requirements in Section C; include WBS</t>
         </is>
       </c>
-      <c r="E16" s="28" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>II — Tech</t>
         </is>
       </c>
-      <c r="F16" s="28" t="inlineStr">
+      <c r="F16" s="36" t="inlineStr">
         <is>
           <t>Vol II, Section 1.0</t>
         </is>
       </c>
-      <c r="G16" s="28" t="inlineStr">
+      <c r="G16" s="36" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="H16" s="29" t="inlineStr">
+      <c r="H16" s="37" t="inlineStr">
         <is>
           <t>WBS diagram in progress; narrative 80% complete</t>
         </is>
       </c>
-      <c r="I16" s="28" t="inlineStr">
+      <c r="I16" s="36" t="inlineStr">
         <is>
           <t>Tech Lead</t>
         </is>
       </c>
-      <c r="J16" s="30" t="n">
+      <c r="J16" s="38" t="n">
         <v>46134</v>
       </c>
+      <c r="K16" s="42">
+        <f>IF(G16="Compliant","",IF(AND(G16&lt;&gt;"N/A",TODAY()&gt;J16),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="19">
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>L-004</t>
         </is>
       </c>
-      <c r="C17" s="28" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>L.5.2.2</t>
         </is>
       </c>
-      <c r="D17" s="29" t="inlineStr">
+      <c r="D17" s="37" t="inlineStr">
         <is>
           <t>Systems Engineering Plan — Describe SE processes, tools, and standards (MIL-STD-882E, IEEE 15288)</t>
         </is>
       </c>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="E17" s="36" t="inlineStr">
         <is>
           <t>II — Tech</t>
         </is>
       </c>
-      <c r="F17" s="28" t="inlineStr">
+      <c r="F17" s="36" t="inlineStr">
         <is>
           <t>Vol II, Section 2.0</t>
         </is>
       </c>
-      <c r="G17" s="28" t="inlineStr">
+      <c r="G17" s="36" t="inlineStr">
         <is>
           <t>Compliant</t>
         </is>
       </c>
-      <c r="H17" s="29" t="inlineStr">
+      <c r="H17" s="37" t="inlineStr">
         <is>
           <t>SE plan aligned with customer standards</t>
         </is>
       </c>
-      <c r="I17" s="28" t="inlineStr">
+      <c r="I17" s="36" t="inlineStr">
         <is>
           <t>Systems Engr</t>
         </is>
       </c>
-      <c r="J17" s="30" t="n">
+      <c r="J17" s="38" t="n">
         <v>46129</v>
       </c>
+      <c r="K17" s="42">
+        <f>IF(G17="Compliant","",IF(AND(G17&lt;&gt;"N/A",TODAY()&gt;J17),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="19">
-      <c r="B18" s="28" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>L-005</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr">
+      <c r="C18" s="36" t="inlineStr">
         <is>
           <t>L.5.2.3</t>
         </is>
       </c>
-      <c r="D18" s="29" t="inlineStr">
+      <c r="D18" s="37" t="inlineStr">
         <is>
           <t>Transition Plan — 90-day transition-in plan with risk mitigation and knowledge transfer approach</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="36" t="inlineStr">
         <is>
           <t>II — Tech</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
+      <c r="F18" s="36" t="inlineStr">
         <is>
           <t>Vol II, Section 3.0</t>
         </is>
       </c>
-      <c r="G18" s="28" t="inlineStr">
+      <c r="G18" s="36" t="inlineStr">
         <is>
           <t>Non-Compliant</t>
         </is>
       </c>
-      <c r="H18" s="29" t="inlineStr">
+      <c r="H18" s="37" t="inlineStr">
         <is>
           <t>Transition timeline draft incomplete; need sub input</t>
         </is>
       </c>
-      <c r="I18" s="28" t="inlineStr">
+      <c r="I18" s="36" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="J18" s="30" t="n">
+      <c r="J18" s="38" t="n">
         <v>46137</v>
       </c>
+      <c r="K18" s="42">
+        <f>IF(G18="Compliant","",IF(AND(G18&lt;&gt;"N/A",TODAY()&gt;J18),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="19">
-      <c r="B19" s="28" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>L-006</t>
         </is>
       </c>
-      <c r="C19" s="28" t="inlineStr">
+      <c r="C19" s="36" t="inlineStr">
         <is>
           <t>L.5.2.4</t>
         </is>
       </c>
-      <c r="D19" s="29" t="inlineStr">
+      <c r="D19" s="37" t="inlineStr">
         <is>
           <t>Cybersecurity Approach — Describe compliance with NIST 800-171 and CMMC Level 2 requirements</t>
         </is>
       </c>
-      <c r="E19" s="28" t="inlineStr">
+      <c r="E19" s="36" t="inlineStr">
         <is>
           <t>II — Tech</t>
         </is>
       </c>
-      <c r="F19" s="28" t="inlineStr">
+      <c r="F19" s="36" t="inlineStr">
         <is>
           <t>Vol II, Section 4.0</t>
         </is>
       </c>
-      <c r="G19" s="28" t="inlineStr">
+      <c r="G19" s="36" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="H19" s="29" t="inlineStr">
+      <c r="H19" s="37" t="inlineStr">
         <is>
           <t>CMMC gap analysis underway; SSP in development</t>
         </is>
       </c>
-      <c r="I19" s="28" t="inlineStr">
+      <c r="I19" s="36" t="inlineStr">
         <is>
           <t>ISSM</t>
         </is>
       </c>
-      <c r="J19" s="30" t="n">
+      <c r="J19" s="38" t="n">
         <v>46135</v>
       </c>
+      <c r="K19" s="42">
+        <f>IF(G19="Compliant","",IF(AND(G19&lt;&gt;"N/A",TODAY()&gt;J19),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="19">
-      <c r="B20" s="28" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr">
         <is>
           <t>L-007</t>
         </is>
       </c>
-      <c r="C20" s="28" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>L.5.2.5</t>
         </is>
       </c>
-      <c r="D20" s="29" t="inlineStr">
+      <c r="D20" s="37" t="inlineStr">
         <is>
           <t>Quality Assurance Surveillance Plan (QASP) — Describe QA processes and metrics tracking</t>
         </is>
       </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>II — Tech</t>
         </is>
       </c>
-      <c r="F20" s="28" t="inlineStr">
+      <c r="F20" s="36" t="inlineStr">
         <is>
           <t>Vol II, Section 5.0</t>
         </is>
       </c>
-      <c r="G20" s="28" t="inlineStr">
+      <c r="G20" s="36" t="inlineStr">
         <is>
           <t>Compliant</t>
         </is>
       </c>
-      <c r="H20" s="29" t="inlineStr">
+      <c r="H20" s="37" t="inlineStr">
         <is>
           <t>QASP aligned with PWS performance standards</t>
         </is>
       </c>
-      <c r="I20" s="28" t="inlineStr">
+      <c r="I20" s="36" t="inlineStr">
         <is>
           <t>QA Lead</t>
         </is>
       </c>
-      <c r="J20" s="30" t="n">
+      <c r="J20" s="38" t="n">
         <v>46128</v>
       </c>
+      <c r="K20" s="42">
+        <f>IF(G20="Compliant","",IF(AND(G20&lt;&gt;"N/A",TODAY()&gt;J20),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="19">
-      <c r="B21" s="28" t="inlineStr">
+      <c r="B21" s="36" t="inlineStr">
         <is>
           <t>L-008</t>
         </is>
       </c>
-      <c r="C21" s="28" t="inlineStr">
+      <c r="C21" s="36" t="inlineStr">
         <is>
           <t>L.5.3.1</t>
         </is>
       </c>
-      <c r="D21" s="29" t="inlineStr">
+      <c r="D21" s="37" t="inlineStr">
         <is>
           <t>Management Approach — Organizational chart, staffing plan, and communication strategy</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E21" s="36" t="inlineStr">
         <is>
           <t>III — Mgmt</t>
         </is>
       </c>
-      <c r="F21" s="28" t="inlineStr">
+      <c r="F21" s="36" t="inlineStr">
         <is>
           <t>Vol III, Section 1.0</t>
         </is>
       </c>
-      <c r="G21" s="28" t="inlineStr">
+      <c r="G21" s="36" t="inlineStr">
         <is>
           <t>Compliant</t>
         </is>
       </c>
-      <c r="H21" s="29" t="inlineStr">
+      <c r="H21" s="37" t="inlineStr">
         <is>
           <t>Org chart finalized; staffing plan approved</t>
         </is>
       </c>
-      <c r="I21" s="28" t="inlineStr">
+      <c r="I21" s="36" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="J21" s="30" t="n">
+      <c r="J21" s="38" t="n">
         <v>46131</v>
       </c>
+      <c r="K21" s="42">
+        <f>IF(G21="Compliant","",IF(AND(G21&lt;&gt;"N/A",TODAY()&gt;J21),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="19">
-      <c r="B22" s="28" t="inlineStr">
+      <c r="B22" s="36" t="inlineStr">
         <is>
           <t>L-009</t>
         </is>
       </c>
-      <c r="C22" s="28" t="inlineStr">
+      <c r="C22" s="36" t="inlineStr">
         <is>
           <t>L.5.3.2</t>
         </is>
       </c>
-      <c r="D22" s="29" t="inlineStr">
+      <c r="D22" s="37" t="inlineStr">
         <is>
           <t>Key Personnel — Resumes for PM, Deputy PM, Technical Lead; 5-page max per resume</t>
         </is>
       </c>
-      <c r="E22" s="28" t="inlineStr">
+      <c r="E22" s="36" t="inlineStr">
         <is>
           <t>III — Mgmt</t>
         </is>
       </c>
-      <c r="F22" s="28" t="inlineStr">
+      <c r="F22" s="36" t="inlineStr">
         <is>
           <t>Vol III, Section 2.0</t>
         </is>
       </c>
-      <c r="G22" s="28" t="inlineStr">
+      <c r="G22" s="36" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="H22" s="29" t="inlineStr">
+      <c r="H22" s="37" t="inlineStr">
         <is>
           <t>PM and Tech Lead resumes ready; Deputy PM TBD</t>
         </is>
       </c>
-      <c r="I22" s="28" t="inlineStr">
+      <c r="I22" s="36" t="inlineStr">
         <is>
           <t>HR/Recruiting</t>
         </is>
       </c>
-      <c r="J22" s="30" t="n">
+      <c r="J22" s="38" t="n">
         <v>46133</v>
       </c>
+      <c r="K22" s="42">
+        <f>IF(G22="Compliant","",IF(AND(G22&lt;&gt;"N/A",TODAY()&gt;J22),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="19">
-      <c r="B23" s="28" t="inlineStr">
+      <c r="B23" s="36" t="inlineStr">
         <is>
           <t>L-010</t>
         </is>
       </c>
-      <c r="C23" s="28" t="inlineStr">
+      <c r="C23" s="36" t="inlineStr">
         <is>
           <t>L.5.3.3</t>
         </is>
       </c>
-      <c r="D23" s="29" t="inlineStr">
+      <c r="D23" s="37" t="inlineStr">
         <is>
           <t>Subcontract Management Plan — Identify major subs; describe oversight and flow-down requirements</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="E23" s="36" t="inlineStr">
         <is>
           <t>III — Mgmt</t>
         </is>
       </c>
-      <c r="F23" s="28" t="inlineStr">
+      <c r="F23" s="36" t="inlineStr">
         <is>
           <t>Vol III, Section 3.0</t>
         </is>
       </c>
-      <c r="G23" s="28" t="inlineStr">
+      <c r="G23" s="36" t="inlineStr">
         <is>
           <t>Compliant</t>
         </is>
       </c>
-      <c r="H23" s="29" t="inlineStr">
+      <c r="H23" s="37" t="inlineStr">
         <is>
           <t>Teaming agreements executed; flow-downs mapped</t>
         </is>
       </c>
-      <c r="I23" s="28" t="inlineStr">
+      <c r="I23" s="36" t="inlineStr">
         <is>
           <t>Subcontracts Mgr</t>
         </is>
       </c>
-      <c r="J23" s="30" t="n">
+      <c r="J23" s="38" t="n">
         <v>46130</v>
       </c>
+      <c r="K23" s="42">
+        <f>IF(G23="Compliant","",IF(AND(G23&lt;&gt;"N/A",TODAY()&gt;J23),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="19">
-      <c r="B24" s="28" t="inlineStr">
+      <c r="B24" s="36" t="inlineStr">
         <is>
           <t>L-011</t>
         </is>
       </c>
-      <c r="C24" s="28" t="inlineStr">
+      <c r="C24" s="36" t="inlineStr">
         <is>
           <t>L.5.4.1</t>
         </is>
       </c>
-      <c r="D24" s="29" t="inlineStr">
+      <c r="D24" s="37" t="inlineStr">
         <is>
           <t>Past Performance — 5 relevant contracts within last 5 years; include CPARS ratings and POC info</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E24" s="36" t="inlineStr">
         <is>
           <t>IV — PP</t>
         </is>
       </c>
-      <c r="F24" s="28" t="inlineStr">
+      <c r="F24" s="36" t="inlineStr">
         <is>
           <t>Vol IV, Section 1.0</t>
         </is>
       </c>
-      <c r="G24" s="28" t="inlineStr">
+      <c r="G24" s="36" t="inlineStr">
         <is>
           <t>Compliant</t>
         </is>
       </c>
-      <c r="H24" s="29" t="inlineStr">
+      <c r="H24" s="37" t="inlineStr">
         <is>
           <t>5 references selected; questionnaires sent</t>
         </is>
       </c>
-      <c r="I24" s="28" t="inlineStr">
+      <c r="I24" s="36" t="inlineStr">
         <is>
           <t>BD Lead</t>
         </is>
       </c>
-      <c r="J24" s="30" t="n">
+      <c r="J24" s="38" t="n">
         <v>46129</v>
       </c>
+      <c r="K24" s="42">
+        <f>IF(G24="Compliant","",IF(AND(G24&lt;&gt;"N/A",TODAY()&gt;J24),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="19">
-      <c r="B25" s="28" t="inlineStr">
+      <c r="B25" s="36" t="inlineStr">
         <is>
           <t>L-012</t>
         </is>
       </c>
-      <c r="C25" s="28" t="inlineStr">
+      <c r="C25" s="36" t="inlineStr">
         <is>
           <t>L.5.4.2</t>
         </is>
       </c>
-      <c r="D25" s="29" t="inlineStr">
+      <c r="D25" s="37" t="inlineStr">
         <is>
           <t>Past Performance Questionnaires — Submit PPQ to each reference; provide completed forms in proposal</t>
         </is>
       </c>
-      <c r="E25" s="28" t="inlineStr">
+      <c r="E25" s="36" t="inlineStr">
         <is>
           <t>IV — PP</t>
         </is>
       </c>
-      <c r="F25" s="28" t="inlineStr">
+      <c r="F25" s="36" t="inlineStr">
         <is>
           <t>Vol IV, Section 2.0</t>
         </is>
       </c>
-      <c r="G25" s="28" t="inlineStr">
+      <c r="G25" s="36" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="H25" s="29" t="inlineStr">
+      <c r="H25" s="37" t="inlineStr">
         <is>
           <t>3 of 5 questionnaires returned; following up on 2</t>
         </is>
       </c>
-      <c r="I25" s="28" t="inlineStr">
+      <c r="I25" s="36" t="inlineStr">
         <is>
           <t>BD Lead</t>
         </is>
       </c>
-      <c r="J25" s="30" t="n">
+      <c r="J25" s="38" t="n">
         <v>46136</v>
       </c>
+      <c r="K25" s="42">
+        <f>IF(G25="Compliant","",IF(AND(G25&lt;&gt;"N/A",TODAY()&gt;J25),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1" s="19">
-      <c r="B26" s="28" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>L-013</t>
         </is>
       </c>
-      <c r="C26" s="28" t="inlineStr">
+      <c r="C26" s="36" t="inlineStr">
         <is>
           <t>L.5.5.1</t>
         </is>
       </c>
-      <c r="D26" s="29" t="inlineStr">
+      <c r="D26" s="37" t="inlineStr">
         <is>
           <t>Cost/Price Volume — Fully loaded labor rates by LCAT; indirect rate build-up; basis of estimate</t>
         </is>
       </c>
-      <c r="E26" s="28" t="inlineStr">
+      <c r="E26" s="36" t="inlineStr">
         <is>
           <t>V — Cost</t>
         </is>
       </c>
-      <c r="F26" s="28" t="inlineStr">
+      <c r="F26" s="36" t="inlineStr">
         <is>
           <t>Vol V, Section 1.0</t>
         </is>
       </c>
-      <c r="G26" s="28" t="inlineStr">
+      <c r="G26" s="36" t="inlineStr">
         <is>
           <t>Compliant</t>
         </is>
       </c>
-      <c r="H26" s="29" t="inlineStr">
+      <c r="H26" s="37" t="inlineStr">
         <is>
           <t>Rate build-up complete; DCAA-auditable format</t>
         </is>
       </c>
-      <c r="I26" s="28" t="inlineStr">
+      <c r="I26" s="36" t="inlineStr">
         <is>
           <t>Finance Dir</t>
         </is>
       </c>
-      <c r="J26" s="30" t="n">
+      <c r="J26" s="38" t="n">
         <v>46132</v>
       </c>
+      <c r="K26" s="42">
+        <f>IF(G26="Compliant","",IF(AND(G26&lt;&gt;"N/A",TODAY()&gt;J26),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="19">
-      <c r="B27" s="28" t="inlineStr">
+      <c r="B27" s="36" t="inlineStr">
         <is>
           <t>L-014</t>
         </is>
       </c>
-      <c r="C27" s="28" t="inlineStr">
+      <c r="C27" s="36" t="inlineStr">
         <is>
           <t>L.5.5.2</t>
         </is>
       </c>
-      <c r="D27" s="29" t="inlineStr">
+      <c r="D27" s="37" t="inlineStr">
         <is>
           <t>Subcontractor Pricing — Include sub cost proposals; adequate price competition or cost analysis</t>
         </is>
       </c>
-      <c r="E27" s="28" t="inlineStr">
+      <c r="E27" s="36" t="inlineStr">
         <is>
           <t>V — Cost</t>
         </is>
       </c>
-      <c r="F27" s="28" t="inlineStr">
+      <c r="F27" s="36" t="inlineStr">
         <is>
           <t>Vol V, Section 2.0</t>
         </is>
       </c>
-      <c r="G27" s="28" t="inlineStr">
+      <c r="G27" s="36" t="inlineStr">
         <is>
           <t>Non-Compliant</t>
         </is>
       </c>
-      <c r="H27" s="29" t="inlineStr">
+      <c r="H27" s="37" t="inlineStr">
         <is>
           <t>Awaiting 2 sub cost proposals; deadline approaching</t>
         </is>
       </c>
-      <c r="I27" s="28" t="inlineStr">
+      <c r="I27" s="36" t="inlineStr">
         <is>
           <t>Subcontracts Mgr</t>
         </is>
       </c>
-      <c r="J27" s="30" t="n">
+      <c r="J27" s="38" t="n">
         <v>46139</v>
       </c>
+      <c r="K27" s="42">
+        <f>IF(G27="Compliant","",IF(AND(G27&lt;&gt;"N/A",TODAY()&gt;J27),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="19">
-      <c r="B28" s="28" t="inlineStr">
+      <c r="B28" s="36" t="inlineStr">
         <is>
           <t>L-015</t>
         </is>
       </c>
-      <c r="C28" s="28" t="inlineStr">
+      <c r="C28" s="36" t="inlineStr">
         <is>
           <t>L.5.6.1</t>
         </is>
       </c>
-      <c r="D28" s="29" t="inlineStr">
+      <c r="D28" s="37" t="inlineStr">
         <is>
           <t>CDRL Deliverables List — Acknowledge all CDRLs in DD Form 1423; provide delivery schedule</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr">
+      <c r="E28" s="36" t="inlineStr">
         <is>
           <t>II — Tech</t>
         </is>
       </c>
-      <c r="F28" s="28" t="inlineStr">
+      <c r="F28" s="36" t="inlineStr">
         <is>
           <t>Vol II, Appendix A</t>
         </is>
       </c>
-      <c r="G28" s="28" t="inlineStr">
+      <c r="G28" s="36" t="inlineStr">
         <is>
           <t>Compliant</t>
         </is>
       </c>
-      <c r="H28" s="29" t="inlineStr">
+      <c r="H28" s="37" t="inlineStr">
         <is>
           <t>All 23 CDRLs mapped and acknowledged</t>
         </is>
       </c>
-      <c r="I28" s="28" t="inlineStr">
+      <c r="I28" s="36" t="inlineStr">
         <is>
           <t>Tech Writer</t>
         </is>
       </c>
-      <c r="J28" s="30" t="n">
+      <c r="J28" s="38" t="n">
         <v>46128</v>
       </c>
+      <c r="K28" s="42">
+        <f>IF(G28="Compliant","",IF(AND(G28&lt;&gt;"N/A",TODAY()&gt;J28),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1" s="19">
-      <c r="B29" s="28" t="inlineStr">
+      <c r="B29" s="36" t="inlineStr">
         <is>
           <t>L-016</t>
         </is>
       </c>
-      <c r="C29" s="28" t="inlineStr">
+      <c r="C29" s="36" t="inlineStr">
         <is>
           <t>L.5.6.2</t>
         </is>
       </c>
-      <c r="D29" s="29" t="inlineStr">
+      <c r="D29" s="37" t="inlineStr">
         <is>
           <t>DD Form 254 — Security Classification Guide acknowledgment; personnel clearance plan</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr">
+      <c r="E29" s="36" t="inlineStr">
         <is>
           <t>I — Admin</t>
         </is>
       </c>
-      <c r="F29" s="28" t="inlineStr">
+      <c r="F29" s="36" t="inlineStr">
         <is>
           <t>Vol I, Section 3.0</t>
         </is>
       </c>
-      <c r="G29" s="28" t="inlineStr">
+      <c r="G29" s="36" t="inlineStr">
         <is>
           <t>Compliant</t>
         </is>
       </c>
-      <c r="H29" s="29" t="inlineStr">
+      <c r="H29" s="37" t="inlineStr">
         <is>
           <t>DD 254 reviewed; FSO coordination complete</t>
         </is>
       </c>
-      <c r="I29" s="28" t="inlineStr">
+      <c r="I29" s="36" t="inlineStr">
         <is>
           <t>FSO</t>
         </is>
       </c>
-      <c r="J29" s="30" t="n">
+      <c r="J29" s="38" t="n">
         <v>46129</v>
       </c>
+      <c r="K29" s="42">
+        <f>IF(G29="Compliant","",IF(AND(G29&lt;&gt;"N/A",TODAY()&gt;J29),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="30" customHeight="1" s="19">
-      <c r="B30" s="28" t="inlineStr">
+      <c r="B30" s="36" t="inlineStr">
         <is>
           <t>L-017</t>
         </is>
       </c>
-      <c r="C30" s="28" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
         <is>
           <t>L.5.7.1</t>
         </is>
       </c>
-      <c r="D30" s="29" t="inlineStr">
+      <c r="D30" s="37" t="inlineStr">
         <is>
           <t>Small Business Subcontracting Plan — Meet or exceed SB goals per FAR 19.704; include ISR/SSR commitment</t>
         </is>
       </c>
-      <c r="E30" s="28" t="inlineStr">
+      <c r="E30" s="36" t="inlineStr">
         <is>
           <t>I — Admin</t>
         </is>
       </c>
-      <c r="F30" s="28" t="inlineStr">
+      <c r="F30" s="36" t="inlineStr">
         <is>
           <t>Vol I, Section 4.0</t>
         </is>
       </c>
-      <c r="G30" s="28" t="inlineStr">
+      <c r="G30" s="36" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="H30" s="29" t="inlineStr">
+      <c r="H30" s="37" t="inlineStr">
         <is>
           <t>SB plan at 35% vs 38% target; identifying additional SBs</t>
         </is>
       </c>
-      <c r="I30" s="28" t="inlineStr">
+      <c r="I30" s="36" t="inlineStr">
         <is>
           <t>SB Liaison</t>
         </is>
       </c>
-      <c r="J30" s="30" t="n">
+      <c r="J30" s="38" t="n">
         <v>46134</v>
       </c>
+      <c r="K30" s="42">
+        <f>IF(G30="Compliant","",IF(AND(G30&lt;&gt;"N/A",TODAY()&gt;J30),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1" s="19">
-      <c r="B31" s="28" t="inlineStr">
+      <c r="B31" s="36" t="inlineStr">
         <is>
           <t>L-018</t>
         </is>
       </c>
-      <c r="C31" s="28" t="inlineStr">
+      <c r="C31" s="36" t="inlineStr">
         <is>
           <t>L.5.7.2</t>
         </is>
       </c>
-      <c r="D31" s="29" t="inlineStr">
+      <c r="D31" s="37" t="inlineStr">
         <is>
           <t>Organizational Conflict of Interest (OCI) — Mitigation plan per FAR 9.5; disclose potential conflicts</t>
         </is>
       </c>
-      <c r="E31" s="28" t="inlineStr">
+      <c r="E31" s="36" t="inlineStr">
         <is>
           <t>I — Admin</t>
         </is>
       </c>
-      <c r="F31" s="28" t="inlineStr">
+      <c r="F31" s="36" t="inlineStr">
         <is>
           <t>Vol I, Section 5.0</t>
         </is>
       </c>
-      <c r="G31" s="28" t="inlineStr">
+      <c r="G31" s="36" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H31" s="29" t="inlineStr">
+      <c r="H31" s="37" t="inlineStr">
         <is>
           <t>No OCIs identified; self-certification letter prepared</t>
         </is>
       </c>
-      <c r="I31" s="28" t="inlineStr">
+      <c r="I31" s="36" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
-      <c r="J31" s="30" t="n">
+      <c r="J31" s="38" t="n">
         <v>46128</v>
       </c>
+      <c r="K31" s="42">
+        <f>IF(G31="Compliant","",IF(AND(G31&lt;&gt;"N/A",TODAY()&gt;J31),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1" s="19">
-      <c r="B32" s="28" t="inlineStr">
+      <c r="B32" s="36" t="inlineStr">
         <is>
           <t>L-019</t>
         </is>
       </c>
-      <c r="C32" s="28" t="inlineStr">
+      <c r="C32" s="36" t="inlineStr">
         <is>
           <t>L.5.8.1</t>
         </is>
       </c>
-      <c r="D32" s="29" t="inlineStr">
+      <c r="D32" s="37" t="inlineStr">
         <is>
           <t>Section 508 Compliance — Describe approach to accessible deliverables per Section 508 of Rehab Act</t>
         </is>
       </c>
-      <c r="E32" s="28" t="inlineStr">
+      <c r="E32" s="36" t="inlineStr">
         <is>
           <t>II — Tech</t>
         </is>
       </c>
-      <c r="F32" s="28" t="inlineStr">
+      <c r="F32" s="36" t="inlineStr">
         <is>
           <t>Vol II, Section 6.0</t>
         </is>
       </c>
-      <c r="G32" s="28" t="inlineStr">
+      <c r="G32" s="36" t="inlineStr">
         <is>
           <t>Compliant</t>
         </is>
       </c>
-      <c r="H32" s="29" t="inlineStr">
+      <c r="H32" s="37" t="inlineStr">
         <is>
           <t>508 compliance plan based on WCAG 2.1 AA</t>
         </is>
       </c>
-      <c r="I32" s="28" t="inlineStr">
+      <c r="I32" s="36" t="inlineStr">
         <is>
           <t>IT Lead</t>
         </is>
       </c>
-      <c r="J32" s="30" t="n">
+      <c r="J32" s="38" t="n">
         <v>46130</v>
       </c>
+      <c r="K32" s="42">
+        <f>IF(G32="Compliant","",IF(AND(G32&lt;&gt;"N/A",TODAY()&gt;J32),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1" s="19">
-      <c r="B33" s="28" t="inlineStr">
+      <c r="B33" s="36" t="inlineStr">
         <is>
           <t>L-020</t>
         </is>
       </c>
-      <c r="C33" s="28" t="inlineStr">
+      <c r="C33" s="36" t="inlineStr">
         <is>
           <t>L.5.8.2</t>
         </is>
       </c>
-      <c r="D33" s="29" t="inlineStr">
+      <c r="D33" s="37" t="inlineStr">
         <is>
           <t>Phase-In/Phase-Out Plan — Describe contractor demobilization and data/IP transfer at contract end</t>
         </is>
       </c>
-      <c r="E33" s="28" t="inlineStr">
+      <c r="E33" s="36" t="inlineStr">
         <is>
           <t>II — Tech</t>
         </is>
       </c>
-      <c r="F33" s="28" t="inlineStr">
+      <c r="F33" s="36" t="inlineStr">
         <is>
           <t>Vol II, Section 7.0</t>
         </is>
       </c>
-      <c r="G33" s="28" t="inlineStr">
+      <c r="G33" s="36" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="H33" s="29" t="inlineStr">
+      <c r="H33" s="37" t="inlineStr">
         <is>
           <t>Phase-out plan outline drafted; detail needed on IP transfer</t>
         </is>
       </c>
-      <c r="I33" s="28" t="inlineStr">
+      <c r="I33" s="36" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="J33" s="30" t="n">
+      <c r="J33" s="38" t="n">
         <v>46135</v>
       </c>
-    </row>
-    <row r="34"/>
-    <row r="35"/>
+      <c r="K33" s="42">
+        <f>IF(G33="Compliant","",IF(AND(G33&lt;&gt;"N/A",TODAY()&gt;J33),"OVERDUE","On track"))</f>
+        <v/>
+      </c>
+    </row>
     <row r="36" ht="15" customHeight="1" s="19">
       <c r="B36" s="31" t="inlineStr">
         <is>
@@ -1630,16 +1895,17 @@
     <row r="37" ht="15" customHeight="1" s="19">
       <c r="B37" s="31" t="inlineStr">
         <is>
-          <t>Generated: April 2026 | Updated: FAC 2025-07</t>
+          <t>Generated: September 2026 | Updated: FAC 2025-06</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="4">
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B5:C5"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B5:C5"/>
     <mergeCell ref="B36:J36"/>
-    <mergeCell ref="B2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="G14:G83">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
@@ -1652,6 +1918,11 @@
       <formula>"Non-Compliant"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K14:K33">
+    <cfRule type="expression" priority="4" dxfId="11">
+      <formula>K14="OVERDUE"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="G14:G83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid status" type="list" errorStyle="stop" operator="between">
       <formula1>"Compliant,Partial,Non-Compliant,N/A"</formula1>
@@ -1660,9 +1931,10 @@
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1674,14 +1946,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="B2:B31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="18" min="1" max="1"/>
     <col width="90" customWidth="1" style="18" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="30" customHeight="1" s="19">
       <c r="B2" s="32" t="inlineStr">
         <is>
@@ -1689,7 +1960,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="24.75" customHeight="1" s="19">
       <c r="B4" s="33" t="inlineStr">
         <is>
@@ -1704,7 +1974,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7" ht="24.75" customHeight="1" s="19">
       <c r="B7" s="33" t="inlineStr">
         <is>
@@ -1775,7 +2044,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="24.75" customHeight="1" s="19">
       <c r="B18" s="33" t="inlineStr">
         <is>
@@ -1832,8 +2100,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="19">
       <c r="B28" s="31" t="inlineStr">
         <is>
@@ -1841,7 +2107,22 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="B30" s="43" t="inlineStr">
+        <is>
+          <t>License &amp; Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="44" t="inlineStr">
+        <is>
+          <t>This template is licensed for use on one program, by one organization, under your Acqlerate purchase. Customize the text, branding, and layout freely for your own program. Deploying it company-wide, sharing it outside your organization, or reselling it requires an Acqlerate Team License (acqlerate.com/team).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="0"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
